--- a/data/daily/2026-08/2026-08-30.xlsx
+++ b/data/daily/2026-08/2026-08-30.xlsx
@@ -1170,14 +1170,39 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1192,17 +1217,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>2</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="352425" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1217,17 +1242,42 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>5</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1242,17 +1292,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1267,17 +1317,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>5</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1292,17 +1342,42 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1317,85 +1392,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
       <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="342900" cy="457200"/>
+    <ext cx="323850" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -1425,77 +1425,127 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="952500" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1503,24 +1553,24 @@
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1528,129 +1578,79 @@
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>10</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
+    <ext cx="866775" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -2976,7 +2976,7 @@
     <row r="15" ht="38" customHeight="1">
       <c r="B15" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2984,34 +2984,34 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>[한끼통살] 닭가슴살 한달 식단패키지 30팩+(증정)보냉백</t>
+          <t>[헬로키티 한정판/단독] 리유저블백&amp;틴케이스 키링 증정, 엑스트라버진 올리브오일 캡슐 30포</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>한끼통살</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>45,800원</t>
+          <t>29,900원</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/11566779</t>
+          <t>https://gift.kakao.com/product/11839566</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260429112212_3e1db89ad7174b6989286381ae7257c6.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260820175751_c5d7886f2f9642b8b4b4d5e38061f2bc.jpg</t>
         </is>
       </c>
     </row>
     <row r="16" ht="38" customHeight="1">
       <c r="B16" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -3019,27 +3019,27 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>[헬로키티 한정판/단독] 리유저블백&amp;틴케이스 키링 증정, 엑스트라버진 올리브오일 캡슐 30포</t>
+          <t>[한끼통살] 닭가슴살 한달 식단패키지 30팩+(증정)보냉백</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>푸드올로지</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>29,900원</t>
+          <t>45,800원</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/11839566</t>
+          <t>https://gift.kakao.com/product/11566779</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260820175751_c5d7886f2f9642b8b4b4d5e38061f2bc.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260429112212_3e1db89ad7174b6989286381ae7257c6.jpg</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
     <row r="19" ht="38" customHeight="1">
       <c r="B19" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -3124,34 +3124,34 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
+          <t>BEST 프로틴모음 [랩노쉬] 프로틴 락커 12종 선물세트 (프로틴 드링크 퍼펙트, 단백쿠키, 단백 쿠키바)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>랩노쉬</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>42,900원</t>
+          <t>20,900원</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/7417420</t>
+          <t>https://gift.kakao.com/product/12052312</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260706153340_3e124da6e254462d9a7efad2521e3b9e.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260723171929_09161ef5007a47039ea2ea7988556deb.jpg</t>
         </is>
       </c>
     </row>
     <row r="20" ht="38" customHeight="1">
       <c r="B20" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -3159,27 +3159,27 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>BEST 프로틴모음 [랩노쉬] 프로틴 락커 12종 선물세트 (프로틴 드링크 퍼펙트, 단백쿠키, 단백 쿠키바)</t>
+          <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>랩노쉬</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>20,900원</t>
+          <t>42,900원</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12052312</t>
+          <t>https://gift.kakao.com/product/7417420</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260723171929_09161ef5007a47039ea2ea7988556deb.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260706153340_3e124da6e254462d9a7efad2521e3b9e.jpg</t>
         </is>
       </c>
     </row>
@@ -3703,32 +3703,32 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="K11" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -3760,14 +3760,14 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
+          <t>푸드올로지</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
           <t>한끼통살</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>푸드올로지</t>
-        </is>
-      </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
           <t>한끼통살</t>
@@ -3780,12 +3780,12 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>랩노쉬</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
           <t>익스트림</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>랩노쉬</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -3817,14 +3817,14 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
+          <t>[헬로키티 한정판/단독] 리유저블백&amp;틴케이스 키링 증정, 엑스트라버진 올리브오일 캡슐 30포</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
           <t>[한끼통살] 닭가슴살 한달 식단패키지 30팩+(증정)보냉백</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>[헬로키티 한정판/단독] 리유저블백&amp;틴케이스 키링 증정, 엑스트라버진 올리브오일 캡슐 30포</t>
-        </is>
-      </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
           <t>[한끼통살] 단백질 든든형 닭가슴살 21일 식단관리+(증정)현미크리스피 닭가슴살 오리지널 1개</t>
@@ -3837,12 +3837,12 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>BEST 프로틴모음 [랩노쉬] 프로틴 락커 12종 선물세트 (프로틴 드링크 퍼펙트, 단백쿠키, 단백 쿠키바)</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
           <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>BEST 프로틴모음 [랩노쉬] 프로틴 락커 12종 선물세트 (프로틴 드링크 퍼펙트, 단백쿠키, 단백 쿠키바)</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -3874,14 +3874,14 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
+          <t>29,900원</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
           <t>45,800원</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>29,900원</t>
-        </is>
-      </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
           <t>32,900원</t>
@@ -3894,12 +3894,12 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>20,900원</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
           <t>42,900원</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>20,900원</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -4054,7 +4054,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -4062,34 +4062,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>비비랩 애사비 탱글 포켓 젤리 사과맛 5포 5일분</t>
+          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>비비랩 (BB LAB)</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994852703&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=944863413&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260615/tjVLFd8X16oPgAvdvPpK994852703_00_00tjVLFd8X16oPgAvdvPpK.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260605/8ADhx4mYwiTujsVcCSTD944863413_00_018ADhx4mYwiTujsVcCSTD.jpg</t>
         </is>
       </c>
     </row>
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -4097,34 +4097,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>종근당건강 락토조이 오늘비움 3병 3일분</t>
+          <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591555314&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000128&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260428/PgvB4Sjc4dtxAp5jXpwI591555314_00_01PgvB4Sjc4dtxAp5jXpwI.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/DZz3h5SxY2J2FqaEB9qZ600000128_00_00DZz3h5SxY2J2FqaEB9qZ.png</t>
         </is>
       </c>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>대웅제약 어린이 칼슘 마그네슘D 츄어블 60정 30일분</t>
+          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -4147,19 +4147,19 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000143&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000145&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/mx3ripII7mLHu95jzlBA600000143_00_00mx3ripII7mLHu95jzlBA.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OHEcumxqCcJ047eosRhh600000145_00_00OHEcumxqCcJ047eosRhh.png</t>
         </is>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -4167,12 +4167,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>종근당건강 눈건강엔 루테인지아잔틴</t>
+          <t>[보령약국 X Pantio] 다이어트 컷 올인원 15포 15일분</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>판티오</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -4182,19 +4182,19 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591580541&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=033991021&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250430/yuK2zGjcuX8RmMDP9k9P591580541_00_00yuK2zGjcuX8RmMDP9k9P.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260805/xVYROwLnuZYLoqWwcjU6033991021_00_00xVYROwLnuZYLoqWwcjU6.png</t>
         </is>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -4202,34 +4202,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>홀베리 레몬 비타C 500 10개입</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>홀베리</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=030086178&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260312/RhgSqjNOPs6aCmkpEpj2030086178_00_00RhgSqjNOPs6aCmkpEpj2.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
         </is>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>대웅제약 비타민C 30정 30일분</t>
+          <t>[우형재 PICK] 익스트림 모노크레아틴 플러스 120 g 40일분</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -4252,19 +4252,19 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000127&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=987253276&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/V0qSVbLLgSaCWbYWEu73600000127_00_00V0qSVbLLgSaCWbYWEu73.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260422/qm625V7JKEa8Iu7GrFAf987253276_00_01qm625V7JKEa8Iu7GrFAf.jpg</t>
         </is>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -4272,34 +4272,34 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>대웅제약 비타민D 4000IU 30정 30일분</t>
+          <t>자연관 이지슬로 엑스트라버진 올리브오일＆레몬 4병</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>자연관</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000132&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032627034&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/SvY5chCvz0QZIyP7AdTc600000132_00_00SvY5chCvz0QZIyP7AdTc.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260810/jotmVom4KndGXbIlPcuj032627034_00_01jotmVom4KndGXbIlPcuj.jpg</t>
         </is>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>대웅제약 칼슘 120정 30일분</t>
+          <t>유한양행 장건강 생유산균 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>유한양행</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000147&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600651649&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250409/7vBQfmyyR1zN9NfVg993600000147_00_007vBQfmyyR1zN9NfVg993.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260325/RN6BLb2wWdxkL0nu9aVK600651649_00_00RN6BLb2wWdxkL0nu9aVK.jpg</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>대웅제약 밀크씨슬 30정 30일분</t>
+          <t>대웅제약 녹차카테킨 30정 30일분</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4357,19 +4357,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000134&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000136&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/bzKNvkJzwy2KdAqrXtDQ600000134_00_00bzKNvkJzwy2KdAqrXtDQ.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/5KgtE2Z5pfS6P1gIBIIh600000136_00_005KgtE2Z5pfS6P1gIBIIh.png</t>
         </is>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -4377,12 +4377,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LG생활건강 이너뷰 콜라겐 더마스틱 7포</t>
+          <t>동국제약 리포좀 비타민C 30정</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>이너뷰 바이 리튠</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -4392,12 +4392,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953528&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910679&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250627/9Cz26kBHEVc4QcQuToeY994953528_00_009Cz26kBHEVc4QcQuToeY.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250829/3zNHA2Xp859SKsazXUwt610910679_00_003zNHA2Xp859SKsazXUwt.png</t>
         </is>
       </c>
     </row>
@@ -4512,52 +4512,52 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>마그네슘</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>루테인/눈건강</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>혈행</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>마그네슘</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>루테인/눈건강</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>비타민C/항산화</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>비타민D</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
         </is>
       </c>
     </row>
@@ -4569,12 +4569,12 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>비비랩 (BB LAB)</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -4584,37 +4584,37 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>판티오</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>홀베리</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
+          <t>익스트림</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>자연관</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>유한양행</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>이너뷰 바이 리튠</t>
+          <t>동국제약</t>
         </is>
       </c>
     </row>
@@ -4626,52 +4626,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>비비랩 애사비 탱글 포켓 젤리 사과맛 5포 5일분</t>
+          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>종근당건강 락토조이 오늘비움 3병 3일분</t>
+          <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 어린이 칼슘 마그네슘D 츄어블 60정 30일분</t>
+          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>종근당건강 눈건강엔 루테인지아잔틴</t>
+          <t>[보령약국 X Pantio] 다이어트 컷 올인원 15포 15일분</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>홀베리 레몬 비타C 500 10개입</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 비타민C 30정 30일분</t>
+          <t>[우형재 PICK] 익스트림 모노크레아틴 플러스 120 g 40일분</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 비타민D 4000IU 30정 30일분</t>
+          <t>자연관 이지슬로 엑스트라버진 올리브오일＆레몬 4병</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 칼슘 120정 30일분</t>
+          <t>유한양행 장건강 생유산균 30캡슐 30일분</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 밀크씨슬 30정 30일분</t>
+          <t>대웅제약 녹차카테킨 30정 30일분</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>LG생활건강 이너뷰 콜라겐 더마스틱 7포</t>
+          <t>동국제약 리포좀 비타민C 30정</t>
         </is>
       </c>
     </row>
@@ -4683,29 +4683,29 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
+          <t>2,000원</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
           <t>3,000원</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>1,000원</t>
-        </is>
-      </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -4875,34 +4875,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[8/30 하루특가/올영단독] 칼로 스탑/컨트롤 PLUS 15포 2종</t>
+          <t>[8/30 하루특가] 리쥬란 이너닷 DNA 글로우 젤리(단품/기획)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>칼로(Kalo)</t>
+          <t>리쥬란</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>8,500원</t>
+          <t>19,700원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000186228&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000258641&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018622891ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0025/A00000025864115ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -4910,27 +4910,27 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+          <t>[웰니스 루틴] 온리추얼 슬리밍컷 다이어트/리셋 브이라인/글로우업 콜라겐 7포(+1포)/14포 (8/14일분)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>지노마스터</t>
+          <t>온리추얼</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>27,400원</t>
+          <t>12,940원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000236701&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492930ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0023/A00000023670137ko.png?l=ko</t>
         </is>
       </c>
     </row>
@@ -4980,27 +4980,27 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[8/30 하루특가] 리쥬란 이너닷 DNA 글로우 젤리(단품/기획)</t>
+          <t>[8/30 하루특가] 코자아 식물성 멜라토닌 함유 젤리/드링크 (단품/기획)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>리쥬란</t>
+          <t>코자아</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>19,700원</t>
+          <t>27,800원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000258641&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000236755&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0025/A00000025864115ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0023/A00000023675539ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
@@ -5015,34 +5015,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[8/30 하루특가] 코자아 식물성 멜라토닌 함유 젤리/드링크 (단품/기획)</t>
+          <t>[스테디셀러 특가] 락토핏 골드 트리플 기획 (3개월분)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>코자아</t>
+          <t>락토핏</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>27,800원</t>
+          <t>17,900원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000236755&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000199062&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0023/A00000023675539ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0019/A00000019906245ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -5050,27 +5050,27 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[파격특가] 콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
+          <t>[스테디셀러특가] [감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>푸드올로지</t>
+          <t>멜라메이트</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>11,900원</t>
+          <t>14,900원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000183645&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018364587ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355463ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
@@ -5085,34 +5085,34 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>판도라 브이트리티 7/14+1포 (7/15일분)</t>
+          <t>[8/30 하루특가/올영단독] 칼로 스탑/컨트롤 PLUS 15포 2종</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>판도라</t>
+          <t>칼로(Kalo)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>24,460원</t>
+          <t>8,500원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000227334&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000186228&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022733450ko.png?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018622891ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -5120,34 +5120,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[9월 올영픽/품절대란] 닥터아돌 카테킨 아세로라 칼시페롤 C D 60정 (+시나모롤 틴케이스 키링)</t>
+          <t>[9월 올영픽] 고려은단 메가도스C 비타민C 3000mg 30포 (+헬로키티 파우치)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>닥터아돌</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>24,900원</t>
+          <t>9,600원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000218073&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000187268&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0021/A00000021807371ko.png?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018726811ko.png?l=ko</t>
         </is>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -5155,34 +5155,34 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[9월 올영픽] 고려은단 메가도스C 비타민C 3000mg 30포 (+헬로키티 파우치)</t>
+          <t>[1일 1정] 바이탈뷰티 메타그린 슬림업 30일 (+15일)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>고려은단</t>
+          <t>바이탈뷰티</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>9,600원</t>
+          <t>26,370원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000187268&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000248462&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018726811ko.png?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024846229ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -5190,27 +5190,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[스테디셀러특가] [감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+          <t>[단독기획] 비비랩 저분자콜라겐S 30포 단품/더블기획 (1개월/2개월분)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>멜라메이트</t>
+          <t>비비랩</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>14,900원</t>
+          <t>22,900원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000208888&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355463ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020888832ko.png?l=ko</t>
         </is>
       </c>
     </row>
@@ -5330,14 +5330,14 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
           <t>프로바이오틱스/유산균</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
@@ -5350,7 +5350,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -5360,17 +5360,17 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>비타민C/항산화</t>
-        </is>
-      </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>피부/미용</t>
         </is>
       </c>
     </row>
@@ -5382,52 +5382,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>리쥬란</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>온리추얼</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>덴프스</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>코자아</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>락토핏</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>멜라메이트</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
           <t>칼로(Kalo)</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>지노마스터</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>덴프스</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>리쥬란</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>코자아</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>푸드올로지</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>판도라</t>
-        </is>
-      </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>닥터아돌</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>고려은단</t>
+          <t>바이탈뷰티</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>멜라메이트</t>
+          <t>비비랩</t>
         </is>
       </c>
     </row>
@@ -5439,52 +5439,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>[8/30 하루특가] 리쥬란 이너닷 DNA 글로우 젤리(단품/기획)</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>[웰니스 루틴] 온리추얼 슬리밍컷 다이어트/리셋 브이라인/글로우업 콜라겐 7포(+1포)/14포 (8/14일분)</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>[8/30 하루특가] 코자아 식물성 멜라토닌 함유 젤리/드링크 (단품/기획)</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>[스테디셀러 특가] 락토핏 골드 트리플 기획 (3개월분)</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>[스테디셀러특가] [감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
           <t>[8/30 하루특가/올영단독] 칼로 스탑/컨트롤 PLUS 15포 2종</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>[8/30 하루특가] 리쥬란 이너닷 DNA 글로우 젤리(단품/기획)</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>[8/30 하루특가] 코자아 식물성 멜라토닌 함유 젤리/드링크 (단품/기획)</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>[파격특가] 콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>판도라 브이트리티 7/14+1포 (7/15일분)</t>
-        </is>
-      </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>[9월 올영픽/품절대란] 닥터아돌 카테킨 아세로라 칼시페롤 C D 60정 (+시나모롤 틴케이스 키링)</t>
+          <t>[9월 올영픽] 고려은단 메가도스C 비타민C 3000mg 30포 (+헬로키티 파우치)</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>[9월 올영픽] 고려은단 메가도스C 비타민C 3000mg 30포 (+헬로키티 파우치)</t>
+          <t>[1일 1정] 바이탈뷰티 메타그린 슬림업 30일 (+15일)</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>[스테디셀러특가] [감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+          <t>[단독기획] 비비랩 저분자콜라겐S 30포 단품/더블기획 (1개월/2개월분)</t>
         </is>
       </c>
     </row>
@@ -5496,52 +5496,52 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
+          <t>19,700원</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>12,940원</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>31,300원</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>27,800원</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>17,900원</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>14,900원</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
           <t>8,500원</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>27,400원</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>31,300원</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>19,700원</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>27,800원</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>11,900원</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>24,460원</t>
-        </is>
-      </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>24,900원</t>
+          <t>9,600원</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>9,600원</t>
+          <t>26,370원</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>14,900원</t>
+          <t>22,900원</t>
         </is>
       </c>
     </row>
@@ -5671,16 +5671,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>40</v>
+        <v>32.5</v>
       </c>
       <c r="D2" t="n">
         <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
         <v>6</v>
@@ -5689,51 +5689,51 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>22.5</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -5743,10 +5743,10 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
         <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
@@ -5755,7 +5755,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -5765,19 +5765,19 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -5790,16 +5790,16 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -5809,10 +5809,10 @@
         <v>2.5</v>
       </c>
       <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
         <v>1</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -5821,7 +5821,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -5831,10 +5831,10 @@
         <v>2.5</v>
       </c>
       <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
         <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -5843,7 +5843,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -5865,7 +5865,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="B11" t="n">
